--- a/output/Results - sem1 (Extended).xlsx
+++ b/output/Results - sem1 (Extended).xlsx
@@ -718,42 +718,42 @@
     <t>NUWANAKA W.A.S.</t>
   </si>
   <si>
+    <t>230077</t>
+  </si>
+  <si>
+    <t>BANDARA K.M.N.D.</t>
+  </si>
+  <si>
+    <t>230444</t>
+  </si>
+  <si>
+    <t>NIRMANI W.T.</t>
+  </si>
+  <si>
+    <t>230727</t>
+  </si>
+  <si>
+    <t>WIJESINGHE W.A.P.W.</t>
+  </si>
+  <si>
+    <t>230238</t>
+  </si>
+  <si>
+    <t>HENDENIYA H.M.J.C.</t>
+  </si>
+  <si>
+    <t>230052</t>
+  </si>
+  <si>
+    <t>ARACHCHIGE M. A. D. T. S.</t>
+  </si>
+  <si>
     <t>230581</t>
   </si>
   <si>
     <t>SANTHOSH S.</t>
   </si>
   <si>
-    <t>230077</t>
-  </si>
-  <si>
-    <t>BANDARA K.M.N.D.</t>
-  </si>
-  <si>
-    <t>230444</t>
-  </si>
-  <si>
-    <t>NIRMANI W.T.</t>
-  </si>
-  <si>
-    <t>230727</t>
-  </si>
-  <si>
-    <t>WIJESINGHE W.A.P.W.</t>
-  </si>
-  <si>
-    <t>230238</t>
-  </si>
-  <si>
-    <t>HENDENIYA H.M.J.C.</t>
-  </si>
-  <si>
-    <t>230052</t>
-  </si>
-  <si>
-    <t>ARACHCHIGE M. A. D. T. S.</t>
-  </si>
-  <si>
     <t>28(24.3%)</t>
   </si>
   <si>
@@ -799,7 +799,7 @@
     <t>11(9.6%)</t>
   </si>
   <si>
-    <t>9(7.8%)</t>
+    <t>8(7.0%)</t>
   </si>
   <si>
     <t>13(11.3%)</t>
@@ -811,10 +811,10 @@
     <t>1(0.9%)</t>
   </si>
   <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
     <t>0(0.0%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
   </si>
   <si>
     <t>B-</t>
@@ -1444,10 +1444,10 @@
         <v>264</v>
       </c>
       <c r="R5" t="s">
+        <v>264</v>
+      </c>
+      <c r="S5" t="s">
         <v>265</v>
-      </c>
-      <c r="S5" t="s">
-        <v>266</v>
       </c>
       <c r="T5" t="s">
         <v>264</v>
@@ -1491,22 +1491,22 @@
         <v>201</v>
       </c>
       <c r="O6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="P6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q6" t="s">
         <v>264</v>
       </c>
       <c r="R6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S6" t="s">
         <v>264</v>
       </c>
       <c r="T6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1547,22 +1547,22 @@
         <v>267</v>
       </c>
       <c r="O7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T7" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -1603,22 +1603,22 @@
         <v>268</v>
       </c>
       <c r="O8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -1659,22 +1659,22 @@
         <v>269</v>
       </c>
       <c r="O9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -1715,22 +1715,22 @@
         <v>270</v>
       </c>
       <c r="O10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -1771,22 +1771,22 @@
         <v>271</v>
       </c>
       <c r="O11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -1827,22 +1827,22 @@
         <v>272</v>
       </c>
       <c r="O12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T12" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -1883,22 +1883,22 @@
         <v>273</v>
       </c>
       <c r="O13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -1939,22 +1939,22 @@
         <v>274</v>
       </c>
       <c r="O14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -1995,22 +1995,22 @@
         <v>275</v>
       </c>
       <c r="O15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -5349,25 +5349,25 @@
         <v>235</v>
       </c>
       <c r="D111" t="s">
-        <v>16</v>
+        <v>201</v>
       </c>
       <c r="E111" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F111" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G111" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>13</v>
       </c>
       <c r="J111">
-        <v>3.792</v>
+        <v>3.785</v>
       </c>
       <c r="K111">
         <v>110</v>
@@ -5375,7 +5375,7 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B112" t="s">
         <v>236</v>
@@ -5384,22 +5384,22 @@
         <v>237</v>
       </c>
       <c r="D112" t="s">
-        <v>201</v>
+        <v>119</v>
       </c>
       <c r="E112" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="F112" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G112" t="s">
         <v>16</v>
       </c>
       <c r="H112" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="I112" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="J112">
         <v>3.785</v>
@@ -5410,7 +5410,7 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
         <v>238</v>
@@ -5419,10 +5419,10 @@
         <v>239</v>
       </c>
       <c r="D113" t="s">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="E113" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
         <v>16</v>
@@ -5431,21 +5431,21 @@
         <v>16</v>
       </c>
       <c r="H113" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="I113" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="J113">
         <v>3.785</v>
       </c>
       <c r="K113">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="114" spans="1:11">
       <c r="A114">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B114" t="s">
         <v>240</v>
@@ -5454,7 +5454,7 @@
         <v>241</v>
       </c>
       <c r="D114" t="s">
-        <v>201</v>
+        <v>182</v>
       </c>
       <c r="E114" t="s">
         <v>16</v>
@@ -5463,19 +5463,19 @@
         <v>16</v>
       </c>
       <c r="G114" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="H114" t="s">
-        <v>16</v>
+        <v>119</v>
       </c>
       <c r="I114" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J114">
-        <v>3.785</v>
+        <v>3.764</v>
       </c>
       <c r="K114">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -5489,25 +5489,25 @@
         <v>243</v>
       </c>
       <c r="D115" t="s">
+        <v>16</v>
+      </c>
+      <c r="E115" t="s">
+        <v>119</v>
+      </c>
+      <c r="F115" t="s">
         <v>182</v>
       </c>
-      <c r="E115" t="s">
-        <v>16</v>
-      </c>
-      <c r="F115" t="s">
-        <v>16</v>
-      </c>
       <c r="G115" t="s">
         <v>119</v>
       </c>
       <c r="H115" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="I115" t="s">
-        <v>13</v>
+        <v>119</v>
       </c>
       <c r="J115">
-        <v>3.764</v>
+        <v>3.75</v>
       </c>
       <c r="K115">
         <v>114</v>
@@ -5530,19 +5530,19 @@
         <v>119</v>
       </c>
       <c r="F116" t="s">
+        <v>16</v>
+      </c>
+      <c r="G116" t="s">
         <v>182</v>
       </c>
-      <c r="G116" t="s">
-        <v>119</v>
-      </c>
       <c r="H116" t="s">
         <v>16</v>
       </c>
       <c r="I116" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="J116">
-        <v>3.75</v>
+        <v>3.735</v>
       </c>
       <c r="K116">
         <v>115</v>
